--- a/output/topology_excel/6603.xlsx
+++ b/output/topology_excel/6603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
@@ -880,21 +880,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
@@ -924,11 +924,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>302</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="F24" t="n">
         <v>16</v>
@@ -968,11 +968,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>207</v>
+        <v>113</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="n">
         <v>4</v>
       </c>
-      <c r="B26" t="n">
-        <v>8</v>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>56</v>
+        <v>302</v>
       </c>
       <c r="F26" t="n">
         <v>16</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c r="F27" t="n">
         <v>16</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>326</v>
+        <v>116</v>
       </c>
       <c r="F29" t="n">
         <v>16</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="F30" t="n">
         <v>16</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>390</v>
+        <v>107</v>
       </c>
       <c r="F32" t="n">
-        <v>294</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="F34" t="n">
         <v>16</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>124</v>
+        <v>371</v>
       </c>
       <c r="F35" t="n">
-        <v>115</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1213,7 +1213,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="F36" t="n">
         <v>16</v>
@@ -1235,7 +1235,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -1257,7 +1257,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="F38" t="n">
-        <v>244</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -1279,7 +1279,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F39" t="n">
         <v>16</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>113</v>
+        <v>315</v>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="F41" t="n">
-        <v>195</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="F42" t="n">
         <v>16</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="F43" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F44" t="n">
         <v>16</v>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F45" t="n">
         <v>16</v>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="F46" t="n">
         <v>16</v>
@@ -1455,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="F48" t="n">
         <v>16</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="F49" t="n">
         <v>16</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="F50" t="n">
         <v>16</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F51" t="n">
         <v>16</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
         <v>17</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F53" t="n">
         <v>16</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>351</v>
+        <v>174</v>
       </c>
       <c r="F54" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="F55" t="n">
         <v>16</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>302</v>
+        <v>207</v>
       </c>
       <c r="F56" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>302</v>
+        <v>115</v>
       </c>
       <c r="F57" t="n">
         <v>16</v>
@@ -1694,24 +1694,112 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>115</v>
+      </c>
+      <c r="F58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>16</v>
+      </c>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>107</v>
+      </c>
+      <c r="F59" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
         <v>19</v>
       </c>
-      <c r="B58" t="n">
-        <v>20</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>107</v>
-      </c>
-      <c r="F58" t="n">
-        <v>16</v>
+      <c r="B60" t="n">
+        <v>20</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>91</v>
+      </c>
+      <c r="F60" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" t="n">
+        <v>21</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>124</v>
+      </c>
+      <c r="F61" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>164</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/6603.xlsx
+++ b/output/topology_excel/6603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>16</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>16</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>16</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>16</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>16</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>16</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>16</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>16</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>16</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>16</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>16</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>16</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>16</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>16</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1045,13 +1107,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1075,6 +1143,8 @@
       <c r="F29" t="n">
         <v>16</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1167,8 @@
       <c r="F30" t="n">
         <v>16</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1191,8 @@
       <c r="F31" t="n">
         <v>16</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1215,8 @@
       <c r="F32" t="n">
         <v>16</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1155,13 +1231,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F33" t="n">
-        <v>55</v>
+        <v>16</v>
+      </c>
+      <c r="G33" t="n">
+        <v>39</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1185,6 +1267,8 @@
       <c r="F34" t="n">
         <v>16</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1291,8 @@
       <c r="F35" t="n">
         <v>16</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1315,8 @@
       <c r="F36" t="n">
         <v>16</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1339,8 @@
       <c r="F37" t="n">
         <v>16</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1363,8 @@
       <c r="F38" t="n">
         <v>16</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1387,8 @@
       <c r="F39" t="n">
         <v>16</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1309,13 +1403,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="F40" t="n">
-        <v>244</v>
+        <v>16</v>
+      </c>
+      <c r="G40" t="n">
+        <v>228</v>
+      </c>
+      <c r="H40" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1337,8 +1437,10 @@
         <v>351</v>
       </c>
       <c r="F41" t="n">
-        <v>64</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1463,8 @@
       <c r="F42" t="n">
         <v>16</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1487,8 @@
       <c r="F43" t="n">
         <v>16</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1511,8 @@
       <c r="F44" t="n">
         <v>16</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1535,8 @@
       <c r="F45" t="n">
         <v>16</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1559,8 @@
       <c r="F46" t="n">
         <v>16</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1583,8 @@
       <c r="F47" t="n">
         <v>16</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1607,8 @@
       <c r="F48" t="n">
         <v>16</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1631,8 @@
       <c r="F49" t="n">
         <v>16</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1655,8 @@
       <c r="F50" t="n">
         <v>16</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1679,8 @@
       <c r="F51" t="n">
         <v>16</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1703,8 @@
       <c r="F52" t="n">
         <v>16</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1727,8 @@
       <c r="F53" t="n">
         <v>16</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1751,8 @@
       <c r="F54" t="n">
         <v>16</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1775,8 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1661,13 +1791,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="F56" t="n">
-        <v>82</v>
+        <v>16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>191</v>
+      </c>
+      <c r="H56" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -1691,6 +1827,8 @@
       <c r="F57" t="n">
         <v>16</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1851,8 @@
       <c r="F58" t="n">
         <v>16</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1875,8 @@
       <c r="F59" t="n">
         <v>16</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1899,8 @@
       <c r="F60" t="n">
         <v>16</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1771,13 +1915,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F61" t="n">
-        <v>115</v>
+        <v>16</v>
+      </c>
+      <c r="G61" t="n">
+        <v>99</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -1801,6 +1951,8 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
